--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,05</t>
+          <t>0,94; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,42</t>
+          <t>2,16; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,2</t>
+          <t>1,9; 3,98</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,16</t>
+          <t>0,32; 2,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,77</t>
+          <t>1,06; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,03</t>
+          <t>0,86; 2,06</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,96</t>
+          <t>1,29; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,3</t>
+          <t>2,66; 6,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,51</t>
+          <t>2,45; 4,6</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,56</t>
+          <t>1,55; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,16</t>
+          <t>0,99; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,0</t>
+          <t>1,58; 4,08</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,91</t>
+          <t>0,68; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,1</t>
+          <t>1,13; 4,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,49</t>
+          <t>1,37; 3,5</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,05</t>
+          <t>1,9; 5,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,55</t>
+          <t>3,37; 6,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,26</t>
+          <t>2,94; 5,18</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,33</t>
+          <t>1,24; 3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,07</t>
+          <t>0,54; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,32</t>
+          <t>0,97; 2,29</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,93</t>
+          <t>0,13; 0,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,06</t>
+          <t>0,72; 2,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,22</t>
+          <t>0,43; 1,25</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,18</t>
+          <t>1,24; 2,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,64</t>
+          <t>1,82; 2,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,3</t>
+          <t>1,65; 2,26</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3151; 12629</t>
+          <t>2930; 12367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6439; 15688</t>
+          <t>6248; 15333</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11482; 25247</t>
+          <t>11431; 23928</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1759; 11222</t>
+          <t>1655; 10976</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5315; 14288</t>
+          <t>5479; 14737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8830; 21021</t>
+          <t>8911; 21290</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3911; 12494</t>
+          <t>4069; 12904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9668; 21925</t>
+          <t>9241; 21286</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15076; 29931</t>
+          <t>16245; 30516</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4394; 23617</t>
+          <t>4840; 21825</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5377; 15017</t>
+          <t>4702; 14035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12755; 31567</t>
+          <t>12444; 32178</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1233; 6977</t>
+          <t>1205; 7160</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2929; 10602</t>
+          <t>2922; 10719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5920; 15270</t>
+          <t>5967; 15299</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5128; 13630</t>
+          <t>5120; 14176</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8773; 16840</t>
+          <t>8672; 16902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15254; 27713</t>
+          <t>15491; 27299</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7166; 20781</t>
+          <t>7738; 21412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4390; 17580</t>
+          <t>4613; 17611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13962; 34148</t>
+          <t>14313; 33752</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1100; 8646</t>
+          <t>1218; 8550</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5507; 14787</t>
+          <t>5135; 14663</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7096; 20068</t>
+          <t>7049; 20539</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>43611; 75307</t>
+          <t>42948; 74293</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67168; 97876</t>
+          <t>67461; 98508</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119339; 164653</t>
+          <t>118415; 162345</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,97</t>
+          <t>0,96; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,29</t>
+          <t>2,05; 5,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,98</t>
+          <t>1,75; 3,66</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,12</t>
+          <t>0,35; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,86</t>
+          <t>1,15; 2,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,06</t>
+          <t>0,87; 2,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,09</t>
+          <t>1,3; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,12</t>
+          <t>2,67; 6,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,6</t>
+          <t>2,29; 4,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,98</t>
+          <t>1,43; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,95</t>
+          <t>1,59; 3,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,08</t>
+          <t>1,78; 4,81</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,02</t>
+          <t>0,59; 3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,14</t>
+          <t>1,79; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,5</t>
+          <t>1,53; 3,51</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,26</t>
+          <t>1,91; 5,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,58</t>
+          <t>3,23; 6,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,18</t>
+          <t>2,86; 5,18</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,43</t>
+          <t>1,27; 3,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,07</t>
+          <t>1,04; 2,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,29</t>
+          <t>1,33; 2,62</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,92</t>
+          <t>0,21; 1,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,04</t>
+          <t>0,81; 2,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,25</t>
+          <t>0,62; 1,47</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,15</t>
+          <t>1,4; 2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,65</t>
+          <t>2,05; 2,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,26</t>
+          <t>1,8; 2,34</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16788</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2930; 12367</t>
+          <t>3061; 12365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6248; 15333</t>
+          <t>6489; 16060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11431; 23928</t>
+          <t>11082; 23240</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>15348</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1655; 10976</t>
+          <t>1873; 12017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5479; 14737</t>
+          <t>6292; 15754</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8911; 21290</t>
+          <t>9387; 24293</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>21636</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4069; 12904</t>
+          <t>4102; 12037</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9241; 21286</t>
+          <t>9500; 21538</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16245; 30516</t>
+          <t>15372; 29575</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>21371</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4840; 21825</t>
+          <t>5339; 25716</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4702; 14035</t>
+          <t>6700; 14654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12444; 32178</t>
+          <t>14136; 38210</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10127</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1205; 7160</t>
+          <t>1214; 7403</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2922; 10719</t>
+          <t>4092; 10706</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5967; 15299</t>
+          <t>6660; 15218</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20677</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5120; 14176</t>
+          <t>5169; 14525</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8672; 16902</t>
+          <t>8527; 17277</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15491; 27299</t>
+          <t>15260; 27690</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>28520</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7738; 21412</t>
+          <t>9122; 24470</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4613; 17611</t>
+          <t>8062; 20228</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14313; 33752</t>
+          <t>19768; 39098</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>15899</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1218; 8550</t>
+          <t>1710; 9465</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5135; 14663</t>
+          <t>6746; 18920</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7049; 20539</t>
+          <t>10119; 23946</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>42948; 74293</t>
+          <t>49532; 79977</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67461; 98508</t>
+          <t>76532; 104053</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118415; 162345</t>
+          <t>130647; 170365</t>
         </is>
       </c>
     </row>
